--- a/storage/assets/webc_excel/WEBC FAJAR LESTARI (START KPB OKT 23).xlsx
+++ b/storage/assets/webc_excel/WEBC FAJAR LESTARI (START KPB OKT 23).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\h720s-itts01\H720_TS03_ARTEAMFS\KPB\PORTAL\WEBC MD START FROM AGUSTUS 2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2245D2E-F000-4944-A375-72AF000BEFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5CBFF6-D7D4-454E-8600-036CA7713FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="844">
   <si>
     <t>nama_region</t>
   </si>
@@ -2549,6 +2549,18 @@
   </si>
   <si>
     <t>TIDAK ADA KPB MEI 2026</t>
+  </si>
+  <si>
+    <t>TIDAK ADA KPB JUNI 2026</t>
+  </si>
+  <si>
+    <t>TIDAK ADA KPB JULI 2026</t>
+  </si>
+  <si>
+    <t>TIDAK ADA KPB AGST 2026</t>
+  </si>
+  <si>
+    <t>TIDAK ADA KPB SEPT 2026</t>
   </si>
 </sst>
 </file>
@@ -2948,7 +2960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R151"/>
+  <dimension ref="A1:R155"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="11.5703125" style="1"/>
@@ -10903,6 +10915,26 @@
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>839</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>843</v>
       </c>
     </row>
   </sheetData>
